--- a/resultados/Resultados_FacebookAI_xlm-roberta-base.xlsx
+++ b/resultados/Resultados_FacebookAI_xlm-roberta-base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UMA\TFG\TFG-Sistema-Recomendacion-Personalidad\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D099E03-9CDE-4766-AD0A-200DACC5B7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEE1A77-F4EC-4020-AF0D-FED4A25DE171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SMOTE" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="304">
   <si>
     <t>Modelos</t>
   </si>
@@ -47,1063 +47,1047 @@
     <t>Matriz Confusion</t>
   </si>
   <si>
-    <t>Regresión Logística E/I</t>
+    <t>0: 0.70
+1: 0.65</t>
+  </si>
+  <si>
+    <t>0: 200
+1: 668</t>
+  </si>
+  <si>
+    <t>0: 0.27
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 120
+1: 748</t>
+  </si>
+  <si>
+    <t>Parametros</t>
+  </si>
+  <si>
+    <t>{'penalty': None, 'C': 9.732719859279047, 'solver': 'lbfgs', 'tol': 0.00010564097578389837, 'class_weight': 'balanced', 'random_state': 42, 'n_jobs': -1, 'max_iter': 5000}</t>
+  </si>
+  <si>
+    <t>0: 0.71
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.79
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.76</t>
+  </si>
+  <si>
+    <t>0: 398
+1: 470</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.68</t>
+  </si>
+  <si>
+    <t>0: 344
+1: 524</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.84</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.23
+1: 0.92</t>
+  </si>
+  <si>
+    <t>{'n_estimators': 352, 'max_depth': 8, 'learning_rate': 0.041694500859353036, 'subsample': 0.6688508428769014, 'colsample_bytree': 0.6246885857257476, 'gamma': 0.6844100651211652, 'tree_method': 'hist', 'device': 'cuda', 'random_state': 42, 'n_jobs': 1}</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.79</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.77</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.60</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.71</t>
+  </si>
+  <si>
+    <t>[[150 50]
+ [269 399]]</t>
+  </si>
+  <si>
+    <t>0: 0.29
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.76</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[75 45]
+ [181 567]]</t>
+  </si>
+  <si>
+    <t>{'loss': 'squared_hinge', 'C': 9.605448156429867, 'tol': 0.0004119653918147926, 'fit_intercept': False, 'random_state': 42, 'class_weight': 'balanced', 'max_iter': 5000}</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.66
+1: 0.57</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.64</t>
+  </si>
+  <si>
+    <t>[[228 116]
+ [225 299]]</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.64
+1: 0.71</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.78</t>
+  </si>
+  <si>
+    <t>[[128 72]
+ [192 476]]</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.15
+1: 0.97</t>
+  </si>
+  <si>
+    <t>[[18 102]
+ [20 728]]</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (256, 128, 64), 'activation': 'tanh', 'solver': 'adam', 'learning_rate': 'constant', 'learning_rate_init': 0.001, 'early_stopping': True, 'max_iter': 6000, 'random_state': 42}</t>
+  </si>
+  <si>
+    <t>0: 0.76
+1: 0.77</t>
+  </si>
+  <si>
+    <t>0: 0.71
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[282 116]
+ [91 379]]</t>
+  </si>
+  <si>
+    <t>0: 0.56
+1: 0.68</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.76</t>
+  </si>
+  <si>
+    <t>[[159 185]
+ [127 397]]</t>
+  </si>
+  <si>
+    <t>0: 0.29
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.63</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.71</t>
+  </si>
+  <si>
+    <t>[[100 100]
+ [245 423]]</t>
+  </si>
+  <si>
+    <t>0: 0.18
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.19
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[23 97]
+ [105 643]]</t>
+  </si>
+  <si>
+    <t>{'n_neighbors': 2, 'weights': 'distance', 'algorithm': 'brute', 'leaf_size': 14, 'metric': 'cosine', 'n_jobs': -1}</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.64</t>
+  </si>
+  <si>
+    <t>[[231 167]
+ [169 301]]</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.63</t>
+  </si>
+  <si>
+    <t>[[153 191]
+ [195 329]]</t>
+  </si>
+  <si>
+    <t>0: 0.27
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.62</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.69</t>
+  </si>
+  <si>
+    <t>[[95 105]
+ [257 411]]</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.35
+1: 0.84</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[42 78]
+ [122 626]]</t>
+  </si>
+  <si>
+    <t>{'criterion': 'gini', 'max_depth': 15, 'min_samples_split': 9, 'min_samples_leaf': 4, 'max_features': None, 'class_weight': None, 'random_state': 42}</t>
+  </si>
+  <si>
+    <t>0: 0.61
+1: 0.69</t>
+  </si>
+  <si>
+    <t>0: 0.65
+1: 0.65</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.67</t>
+  </si>
+  <si>
+    <t>[[259 139]
+ [166 304]]</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.66</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.67</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.67</t>
+  </si>
+  <si>
+    <t>[[163 181]
+ [172 352]]</t>
+  </si>
+  <si>
+    <t>LR E/I</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.74</t>
+  </si>
+  <si>
+    <t>[[141 59]
+ [237 431]]</t>
+  </si>
+  <si>
+    <t>LR S/N</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.72</t>
+  </si>
+  <si>
+    <t>[[75 45]
+ [213 535]]</t>
+  </si>
+  <si>
+    <t>LR T/F</t>
+  </si>
+  <si>
+    <t>[[314 84]
+ [129 341]]</t>
+  </si>
+  <si>
+    <t>LR J/P</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.70</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.65</t>
+  </si>
+  <si>
+    <t>[[200 144]
+ [182 342]]</t>
+  </si>
+  <si>
+    <t>XGB E/I</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.78</t>
+  </si>
+  <si>
+    <t>[[110 90]
+ [179 489]]</t>
+  </si>
+  <si>
+    <t>XGB S/N</t>
+  </si>
+  <si>
+    <t>0: 0.14
+1: 0.97</t>
+  </si>
+  <si>
+    <t>0: 0.21
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[17 103]
+ [22 726]]</t>
+  </si>
+  <si>
+    <t>XGB T/F</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[297 101]
+ [110 360]]</t>
+  </si>
+  <si>
+    <t>XGB J/P</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.66</t>
+  </si>
+  <si>
+    <t>0: 0.33
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.74</t>
+  </si>
+  <si>
+    <t>[[112 232]
+ [80 444]]</t>
+  </si>
+  <si>
+    <t>LSVC E/I</t>
+  </si>
+  <si>
+    <t>LSVC S/N</t>
+  </si>
+  <si>
+    <t>LSVC T/F</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.96</t>
+  </si>
+  <si>
+    <t>0: 0.99
+1: 0.21</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.35</t>
+  </si>
+  <si>
+    <t>[[394 4]
+ [370 100]]</t>
+  </si>
+  <si>
+    <t>LSVC J/P</t>
+  </si>
+  <si>
+    <t>MLPC E/I</t>
+  </si>
+  <si>
+    <t>MLPC S/N</t>
+  </si>
+  <si>
+    <t>MLPC T/F</t>
+  </si>
+  <si>
+    <t>MLPC J/P</t>
+  </si>
+  <si>
+    <t>KNC E/I</t>
+  </si>
+  <si>
+    <t>KNC S/N</t>
+  </si>
+  <si>
+    <t>KNC T/F</t>
+  </si>
+  <si>
+    <t>KNC J/P</t>
+  </si>
+  <si>
+    <t>DTC E/I</t>
+  </si>
+  <si>
+    <t>DTC S/N</t>
+  </si>
+  <si>
+    <t>DTC T/F</t>
+  </si>
+  <si>
+    <t>DTC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.79</t>
+  </si>
+  <si>
+    <t>0: 0.27
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.69
+1: 0.68</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.77</t>
+  </si>
+  <si>
+    <t>0: 0.22
+1: 0.96</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[109 91]
+ [127 541]]</t>
+  </si>
+  <si>
+    <t>0: 0.29
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.84</t>
+  </si>
+  <si>
+    <t>0: 0.80
+1: 0.31</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.45</t>
+  </si>
+  <si>
+    <t>[[160 40]
+ [462 206]]</t>
+  </si>
+  <si>
+    <t>0: 0.16
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.37</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.53</t>
+  </si>
+  <si>
+    <t>[[89 31]
+ [470 278]]</t>
+  </si>
+  <si>
+    <t>0: 0.28
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.60</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.69</t>
+  </si>
+  <si>
+    <t>[[103 97]
+ [266 402]]</t>
+  </si>
+  <si>
+    <t>0: 0.17
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.70</t>
+  </si>
+  <si>
+    <t>0: 0.23
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[46 74]
+ [228 520]]</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.59
+1: 0.73</t>
+  </si>
+  <si>
+    <t>[[118 82]
+ [181 487]]</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.76</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[66 54]
+ [179 569]]</t>
+  </si>
+  <si>
+    <t>0: 0.43
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.33
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[65 135]
+ [85 583]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.32
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[31 89]
+ [42 706]]</t>
+  </si>
+  <si>
+    <t>[[138 62]
+ [214 454]]</t>
+  </si>
+  <si>
+    <t>0: 0.20
+1: 0.96</t>
+  </si>
+  <si>
+    <t>0: 0.88
+1: 0.45</t>
+  </si>
+  <si>
+    <t>0: 0.33
+1: 0.61</t>
+  </si>
+  <si>
+    <t>[[105 15]
+ [411 337]]</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[66 54]
+ [154 594]]</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.29
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.93
+1: 0.35</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.52</t>
+  </si>
+  <si>
+    <t>[[185 15]
+ [431 237]]</t>
+  </si>
+  <si>
+    <t>0: 0.32
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.64
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 0.43
+1: 0.85</t>
+  </si>
+  <si>
+    <t>[[77 43]
+ [163 585]]</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[121 79]
+ [182 486]]</t>
+  </si>
+  <si>
+    <t>0: 0.27
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.83
+1: 0.31</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.46</t>
+  </si>
+  <si>
+    <t>[[167 33]
+ [461 207]]</t>
+  </si>
+  <si>
+    <t>0: 0.15
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.68
+1: 0.40</t>
+  </si>
+  <si>
+    <t>0: 0.25
+1: 0.55</t>
+  </si>
+  <si>
+    <t>[[82 38]
+ [449 299]]</t>
+  </si>
+  <si>
+    <t>0: 0.16
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.69</t>
+  </si>
+  <si>
+    <t>0: 0.22
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[44 76]
+ [229 519]]</t>
+  </si>
+  <si>
+    <t>[[120 80]
+ [184 484]]</t>
+  </si>
+  <si>
+    <t>0: 0.28
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.54
+1: 0.78</t>
+  </si>
+  <si>
+    <t>[[65 55]
+ [168 580]]</t>
+  </si>
+  <si>
+    <t>0: 0.41
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[75 125]
+ [89 579]]</t>
+  </si>
+  <si>
+    <t>0: 0.28
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.33
+1: 0.91</t>
+  </si>
+  <si>
+    <t>[[33 87]
+ [49 699]]</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[47 73]
+ [92 656]]</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.65</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.72</t>
+  </si>
+  <si>
+    <t>[[98 102]
+ [235 433]]</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.78</t>
+  </si>
+  <si>
+    <t>[[114 86]
+ [184 484]]</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.23
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.31
+1: 0.95</t>
+  </si>
+  <si>
+    <t>0: 0.93
+1: 0.39</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.55</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.67
+1: 0.68</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[134 66]
+ [211 457]]</t>
+  </si>
+  <si>
+    <t>0: 0.25
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.71</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.25
+1: 0.83</t>
+  </si>
+  <si>
+    <t>0: 0.81
+1: 0.29</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.43</t>
+  </si>
+  <si>
+    <t>[[161 39]
+ [476 192]]</t>
+  </si>
+  <si>
+    <t>0: 0.16
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.36</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.51</t>
+  </si>
+  <si>
+    <t>[[88 32]
+ [478 270]]</t>
+  </si>
+  <si>
+    <t>0: 0.51
+1: 0.63</t>
+  </si>
+  <si>
+    <t>[[101 99]
+ [250 418]]</t>
+  </si>
+  <si>
+    <t>0: 0.19
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.68</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[54 66]
+ [236 512]]</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.75</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.82</t>
+  </si>
+  <si>
+    <t>[[66 54]
+ [185 563]]</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.83</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[79 121]
+ [93 575]]</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.88</t>
+  </si>
+  <si>
+    <t>[[28 92]
+ [42 706]]</t>
+  </si>
+  <si>
+    <t>[[185 15]
+ [409 259]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.91</t>
+  </si>
+  <si>
+    <t>[[41 79]
+ [56 692]]</t>
+  </si>
+  <si>
+    <t>[[74 46]
+ [219 529]]</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.65
+1: 0.69</t>
   </si>
   <si>
     <t>0: 0.48
 1: 0.77</t>
   </si>
   <si>
-    <t>Regresión Logística S/N</t>
-  </si>
-  <si>
-    <t>Parametros</t>
-  </si>
-  <si>
-    <t>Regresión Logística T/F</t>
-  </si>
-  <si>
-    <t>Regresión Logística J/P</t>
-  </si>
-  <si>
-    <t>XGBoost E/I</t>
-  </si>
-  <si>
-    <t>XGBoost S/N</t>
-  </si>
-  <si>
-    <t>XGBoost T/F</t>
-  </si>
-  <si>
-    <t>XGBoost J/P</t>
-  </si>
-  <si>
-    <t>LinearSVM E/I</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.78</t>
-  </si>
-  <si>
-    <t>LinearSVM S/N</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.76</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.83</t>
-  </si>
-  <si>
-    <t>LinearSVM T/F</t>
-  </si>
-  <si>
-    <t>LinearSVM J/P</t>
-  </si>
-  <si>
-    <t>MLP E/I</t>
-  </si>
-  <si>
-    <t>MLP S/N</t>
-  </si>
-  <si>
-    <t>MLP T/F</t>
-  </si>
-  <si>
-    <t>MLP J/P</t>
-  </si>
-  <si>
-    <t>{'penalty': None, 'C': 9.732719859279047, 'solver': 'lbfgs', 'tol': 0.00010564097578389837, 'class_weight': 'balanced', 'random_state': 42, 'n_jobs': -1, 'max_iter': 5000}</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.85</t>
-  </si>
-  <si>
-    <t>0: 0.58
-1: 0.73</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.79</t>
-  </si>
-  <si>
-    <t>0: 200
-1: 668</t>
-  </si>
-  <si>
-    <t>[[116 84]
- [180 488]]</t>
-  </si>
-  <si>
-    <t>0: 0.27
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 120
-1: 748</t>
-  </si>
-  <si>
-    <t>[[67 53]
- [179 569]]</t>
-  </si>
-  <si>
-    <t>0: 0.71
-1: 0.80</t>
-  </si>
-  <si>
-    <t>0: 0.79
-1: 0.73</t>
-  </si>
-  <si>
-    <t>0: 0.75
-1: 0.76</t>
-  </si>
-  <si>
-    <t>0: 398
-1: 470</t>
-  </si>
-  <si>
-    <t>[[313 85]
- [129 341]]</t>
-  </si>
-  <si>
-    <t>0: 0.52
-1: 0.71</t>
-  </si>
-  <si>
-    <t>0: 0.59
-1: 0.65</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.68</t>
-  </si>
-  <si>
-    <t>0: 344
-1: 524</t>
-  </si>
-  <si>
-    <t>[[202 142]
- [183 341]]</t>
-  </si>
-  <si>
-    <t>{'n_estimators': 352, 'max_depth': 8, 'learning_rate': 0.041694500859353036, 'subsample': 0.6688508428769014, 'colsample_bytree': 0.6246885857257476, 'gamma': 0.6844100651211652, 'tree_method': 'hist', 'device': 'cuda', 'random_state': 42, 'n_jobs': 1}</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 0.35
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.84</t>
-  </si>
-  <si>
-    <t>[[70 130]
- [87 581]]</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.24
-1: 0.94</t>
-  </si>
-  <si>
-    <t>0: 0.30
-1: 0.91</t>
-  </si>
-  <si>
-    <t>[[29 91]
- [43 705]]</t>
-  </si>
-  <si>
-    <t>0: 0.73
-1: 0.79</t>
-  </si>
-  <si>
-    <t>0: 0.76
-1: 0.76</t>
-  </si>
-  <si>
-    <t>0: 0.74
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[301 97]
- [113 357]]</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.65</t>
-  </si>
-  <si>
-    <t>0: 0.29
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.74</t>
-  </si>
-  <si>
-    <t>[[99 245]
- [75 449]]</t>
-  </si>
-  <si>
-    <t>{'loss': 'squared_hinge', 'C': 9.605448156429867, 'tol': 0.0004119653918147926, 'fit_intercept': False, 'random_state': 42, 'class_weight': 'balanced', 'max_iter': 5000}</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.69
-1: 0.68</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[138 62]
- [213 455]]</t>
-  </si>
-  <si>
-    <t>0: 0.22
-1: 0.96</t>
-  </si>
-  <si>
-    <t>0: 0.86
-1: 0.51</t>
-  </si>
-  <si>
-    <t>0: 0.35
-1: 0.67</t>
-  </si>
-  <si>
-    <t>[[103 17]
- [364 384]]</t>
-  </si>
-  <si>
-    <t>0: 0.82
-1: 0.71</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.66
-1: 0.79</t>
-  </si>
-  <si>
-    <t>[[223 175]
- [50 420]]</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.72</t>
-  </si>
-  <si>
-    <t>0: 0.66
-1: 0.57</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.64</t>
-  </si>
-  <si>
-    <t>[[228 116]
- [225 299]]</t>
-  </si>
-  <si>
-    <t>{'hidden_layer_sizes': (256, 128, 64), 'activation': 'tanh', 'solver': 'adam', 'learning_rate': 'constant', 'learning_rate_init': 0.001, 'early_stopping': True, 'max_iter': 6000, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.83</t>
-  </si>
-  <si>
-    <t>[[109 91]
- [127 541]]</t>
-  </si>
-  <si>
-    <t>0: 0.29
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.79</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.85</t>
-  </si>
-  <si>
-    <t>[[63 57]
- [154 594]]</t>
-  </si>
-  <si>
-    <t>0: 0.76
-1: 0.77</t>
-  </si>
-  <si>
-    <t>0: 0.71
-1: 0.81</t>
-  </si>
-  <si>
-    <t>[[282 116]
- [91 379]]</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.68</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.76</t>
-  </si>
-  <si>
-    <t>[[159 185]
- [127 397]]</t>
-  </si>
-  <si>
-    <t>{'n_neighbors': 2, 'weights': 'distance', 'algorithm': 'brute', 'leaf_size': 14, 'metric': 'cosine', 'n_jobs': -1}</t>
-  </si>
-  <si>
-    <t>KNeighboursClassifier E/I</t>
-  </si>
-  <si>
-    <t>0: 0.26
-1: 0.84</t>
-  </si>
-  <si>
-    <t>0: 0.80
-1: 0.31</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.45</t>
-  </si>
-  <si>
-    <t>[[160 40]
- [462 206]]</t>
-  </si>
-  <si>
-    <t>KNeighboursClassifier S/N</t>
-  </si>
-  <si>
-    <t>0: 0.16
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.74
-1: 0.37</t>
-  </si>
-  <si>
-    <t>0: 0.26
-1: 0.53</t>
-  </si>
-  <si>
-    <t>[[89 31]
- [470 278]]</t>
-  </si>
-  <si>
-    <t>KNeighboursClassifier T/F</t>
-  </si>
-  <si>
-    <t>0: 0.58
-1: 0.64</t>
-  </si>
-  <si>
-    <t>[[231 167]
- [169 301]]</t>
-  </si>
-  <si>
-    <t>KNeighboursClassifier J/P</t>
-  </si>
-  <si>
-    <t>0: 0.44
-1: 0.63</t>
-  </si>
-  <si>
-    <t>[[153 191]
- [195 329]]</t>
-  </si>
-  <si>
-    <t>{'criterion': 'gini', 'max_depth': 15, 'min_samples_split': 9, 'min_samples_leaf': 4, 'max_features': None, 'class_weight': None, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>DecisionTreeClassifier E/I</t>
-  </si>
-  <si>
-    <t>0: 0.28
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 0.52
-1: 0.60</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.69</t>
-  </si>
-  <si>
-    <t>[[103 97]
- [266 402]]</t>
-  </si>
-  <si>
-    <t>DecisionTreeClassifier S/N</t>
-  </si>
-  <si>
-    <t>0: 0.17
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.70</t>
-  </si>
-  <si>
-    <t>0: 0.23
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[46 74]
- [228 520]]</t>
-  </si>
-  <si>
-    <t>DecisionTreeClassifier T/F</t>
-  </si>
-  <si>
-    <t>0: 0.61
-1: 0.69</t>
-  </si>
-  <si>
-    <t>0: 0.65
-1: 0.65</t>
-  </si>
-  <si>
-    <t>0: 0.63
-1: 0.67</t>
-  </si>
-  <si>
-    <t>[[259 139]
- [166 304]]</t>
-  </si>
-  <si>
-    <t>DecisionTreeClassifier J/P</t>
-  </si>
-  <si>
-    <t>0: 0.49
-1: 0.66</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.67</t>
-  </si>
-  <si>
-    <t>0: 0.48
-1: 0.67</t>
-  </si>
-  <si>
-    <t>[[163 181]
- [172 352]]</t>
-  </si>
-  <si>
-    <t>0: 0.29
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.72</t>
-  </si>
-  <si>
-    <t>[[120 80]
- [187 481]]</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.78</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.84</t>
-  </si>
-  <si>
-    <t>[[66 54]
- [164 584]]</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.41
-1: 0.85</t>
-  </si>
-  <si>
-    <t>[[75 125]
- [87 581]]</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.27
-1: 0.94</t>
-  </si>
-  <si>
-    <t>0: 0.32
-1: 0.91</t>
-  </si>
-  <si>
-    <t>[[32 88]
- [45 703]]</t>
-  </si>
-  <si>
-    <t>0: 0.30
-1: 0.94</t>
-  </si>
-  <si>
-    <t>0: 0.93
-1: 0.35</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.52</t>
-  </si>
-  <si>
-    <t>[[185 15]
- [431 237]]</t>
-  </si>
-  <si>
-    <t>0: 0.32
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.64
-1: 0.78</t>
-  </si>
-  <si>
-    <t>0: 0.43
-1: 0.85</t>
-  </si>
-  <si>
-    <t>[[77 43]
- [163 585]]</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.73</t>
-  </si>
-  <si>
-    <t>0: 0.48
-1: 0.79</t>
-  </si>
-  <si>
-    <t>[[121 79]
- [182 486]]</t>
-  </si>
-  <si>
-    <t>0: 0.32
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.88</t>
-  </si>
-  <si>
-    <t>[[52 68]
- [110 638]]</t>
-  </si>
-  <si>
-    <t>0: 0.27
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.83
-1: 0.31</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.46</t>
-  </si>
-  <si>
-    <t>[[167 33]
- [461 207]]</t>
-  </si>
-  <si>
-    <t>0: 0.15
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.68
-1: 0.40</t>
-  </si>
-  <si>
-    <t>0: 0.25
-1: 0.55</t>
-  </si>
-  <si>
-    <t>[[82 38]
- [449 299]]</t>
-  </si>
-  <si>
-    <t>0: 0.32
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 0.52
-1: 0.67</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.74</t>
-  </si>
-  <si>
-    <t>[[104 96]
- [223 445]]</t>
-  </si>
-  <si>
-    <t>0: 0.16
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.69</t>
-  </si>
-  <si>
-    <t>0: 0.22
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[44 76]
- [229 519]]</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.49
-1: 0.77</t>
-  </si>
-  <si>
-    <t>0: 0.34
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.85</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.72</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.78</t>
-  </si>
-  <si>
-    <t>[[114 86]
- [184 484]]</t>
-  </si>
-  <si>
-    <t>0: 0.27
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.76</t>
-  </si>
-  <si>
-    <t>[[68 52]
- [183 565]]</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.84</t>
-  </si>
-  <si>
-    <t>[[67 133]
- [92 576]]</t>
-  </si>
-  <si>
-    <t>0: 0.23
-1: 0.94</t>
-  </si>
-  <si>
-    <t>[[28 92]
- [44 704]]</t>
-  </si>
-  <si>
-    <t>0: 0.31
-1: 0.95</t>
-  </si>
-  <si>
-    <t>0: 0.93
-1: 0.39</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.55</t>
-  </si>
-  <si>
-    <t>[[185 15]
- [408 260]]</t>
-  </si>
-  <si>
-    <t>0: 0.43
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.91</t>
-  </si>
-  <si>
-    <t>[[45 75]
- [60 688]]</t>
-  </si>
-  <si>
-    <t>0: 0.67
-1: 0.68</t>
-  </si>
-  <si>
-    <t>[[134 66]
- [211 457]]</t>
-  </si>
-  <si>
-    <t>0: 0.25
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.62
-1: 0.71</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.80</t>
-  </si>
-  <si>
-    <t>[[74 46]
- [218 530]]</t>
-  </si>
-  <si>
-    <t>0: 0.25
-1: 0.83</t>
-  </si>
-  <si>
-    <t>0: 0.81
-1: 0.29</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.43</t>
-  </si>
-  <si>
-    <t>[[161 39]
- [476 192]]</t>
-  </si>
-  <si>
-    <t>0: 0.16
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.73
-1: 0.36</t>
-  </si>
-  <si>
-    <t>0: 0.26
-1: 0.51</t>
-  </si>
-  <si>
-    <t>[[88 32]
- [478 270]]</t>
-  </si>
-  <si>
-    <t>0: 0.29
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 0.51
-1: 0.63</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.71</t>
-  </si>
-  <si>
-    <t>[[101 99]
- [250 418]]</t>
-  </si>
-  <si>
-    <t>0: 0.19
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.68</t>
-  </si>
-  <si>
-    <t>0: 0.26
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[54 66]
- [236 512]]</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.70
-1: 0.65</t>
-  </si>
-  <si>
-    <t>0: 0.49
-1: 0.75</t>
-  </si>
-  <si>
-    <t>[[140 60]
- [233 435]]</t>
-  </si>
-  <si>
-    <t>0: 0.63
-1: 0.72</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.81</t>
-  </si>
-  <si>
-    <t>[[76 44]
- [210 538]]</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.74</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.79</t>
-  </si>
-  <si>
-    <t>[[109 91]
- [176 492]]</t>
-  </si>
-  <si>
-    <t>0: 0.44
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.16
-1: 0.97</t>
-  </si>
-  <si>
-    <t>0: 0.23
-1: 0.92</t>
-  </si>
-  <si>
-    <t>[[19 101]
- [24 724]]</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.75
-1: 0.60</t>
-  </si>
-  <si>
-    <t>0: 0.48
-1: 0.71</t>
-  </si>
-  <si>
-    <t>[[150 50]
- [269 399]]</t>
-  </si>
-  <si>
-    <t>0: 0.29
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.62
-1: 0.76</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.83</t>
-  </si>
-  <si>
-    <t>[[75 45]
- [181 567]]</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.64
-1: 0.71</t>
-  </si>
-  <si>
-    <t>0: 0.49
-1: 0.78</t>
-  </si>
-  <si>
-    <t>[[128 72]
- [192 476]]</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.15
-1: 0.97</t>
-  </si>
-  <si>
-    <t>[[18 102]
- [20 728]]</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.63</t>
-  </si>
-  <si>
-    <t>[[100 100]
- [245 423]]</t>
-  </si>
-  <si>
-    <t>0: 0.18
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.19
-1: 0.86</t>
-  </si>
-  <si>
-    <t>[[23 97]
- [105 643]]</t>
-  </si>
-  <si>
-    <t>0: 0.27
-1: 0.80</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.62</t>
-  </si>
-  <si>
-    <t>0: 0.34
-1: 0.69</t>
-  </si>
-  <si>
-    <t>[[95 105]
- [257 411]]</t>
-  </si>
-  <si>
-    <t>0: 0.26
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.35
-1: 0.84</t>
-  </si>
-  <si>
-    <t>0: 0.30
-1: 0.86</t>
-  </si>
-  <si>
-    <t>[[42 78]
- [122 626]]</t>
-  </si>
-  <si>
-    <t>0: 0.49
-1: 0.72</t>
-  </si>
-  <si>
-    <t>[[150 50]
- [265 403]]</t>
-  </si>
-  <si>
-    <t>0: 0.26
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.80</t>
-  </si>
-  <si>
-    <t>[[75 45]
- [215 533]]</t>
-  </si>
-  <si>
-    <t>0: 0.69
-1: 0.61</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.72</t>
-  </si>
-  <si>
-    <t>[[137 63]
- [258 410]]</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.19
-1: 0.95</t>
-  </si>
-  <si>
-    <t>[[23 97]
- [35 713]]</t>
-  </si>
-  <si>
-    <t>0: 0.65
-1: 0.69</t>
-  </si>
-  <si>
     <t>[[130 70]
  [208 460]]</t>
   </si>
@@ -1190,6 +1174,34 @@
   <si>
     <t>[[41 79]
  [162 586]]</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.61</t>
+  </si>
+  <si>
+    <t>[[150 50]
+ [263 405]]</t>
+  </si>
+  <si>
+    <t>[[75 45]
+ [207 541]]</t>
+  </si>
+  <si>
+    <t>0: 0.67
+1: 0.62</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.72</t>
+  </si>
+  <si>
+    <t>[[134 66]
+ [257 411]]</t>
+  </si>
+  <si>
+    <t>[[26 94]
+ [33 715]]</t>
   </si>
 </sst>
 </file>
@@ -1693,25 +1705,25 @@
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6">
         <v>0.7</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1720,56 +1732,56 @@
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F5" s="6">
         <v>0.73</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F6" s="6">
         <v>0.75</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1778,25 +1790,25 @@
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F7" s="6">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -1818,25 +1830,25 @@
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>50</v>
+        <v>171</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F9" s="8">
         <v>0.75</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>51</v>
+        <v>172</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1845,56 +1857,56 @@
     </row>
     <row r="10" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>52</v>
+        <v>173</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F10" s="8">
         <v>0.85</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>55</v>
+        <v>176</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F11" s="8">
         <v>0.76</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1903,25 +1915,25 @@
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F12" s="8">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1943,25 +1955,25 @@
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F14" s="10">
         <v>0.68</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1970,56 +1982,56 @@
     </row>
     <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F15" s="10">
-        <v>0.56000000000000005</v>
+        <v>0.51</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F16" s="10">
-        <v>0.74</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -2028,25 +2040,25 @@
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F17" s="10">
         <v>0.61</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -2068,25 +2080,25 @@
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F19" s="12">
         <v>0.75</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -2095,56 +2107,56 @@
     </row>
     <row r="20" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F20" s="12">
         <v>0.76</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F21" s="12">
         <v>0.76</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2153,25 +2165,25 @@
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F22" s="12">
         <v>0.64</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -2191,112 +2203,112 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F24" s="14">
         <v>0.42</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F25" s="14">
         <v>0.42</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F26" s="14">
         <v>0.61</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F27" s="14">
         <v>0.56000000000000005</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2316,112 +2328,112 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F29" s="16">
         <v>0.57999999999999996</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F30" s="16">
         <v>0.65</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F31" s="16">
         <v>0.65</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F32" s="16">
         <v>0.59</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2469,25 +2481,25 @@
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -2496,56 +2508,56 @@
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F5" s="6">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>140</v>
+        <v>216</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F6" s="6">
         <v>0.75</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -2554,25 +2566,25 @@
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F7" s="6">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -2594,25 +2606,25 @@
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>143</v>
+        <v>217</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F9" s="8">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>144</v>
+        <v>218</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -2621,56 +2633,56 @@
     </row>
     <row r="10" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F10" s="8">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>148</v>
+        <v>221</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F11" s="8">
         <v>0.76</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -2679,25 +2691,25 @@
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F12" s="8">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -2719,25 +2731,25 @@
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>151</v>
+        <v>191</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F14" s="10">
         <v>0.49</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -2746,56 +2758,56 @@
     </row>
     <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F15" s="10">
         <v>0.76</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F16" s="10">
-        <v>0.74</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -2804,25 +2816,25 @@
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F17" s="10">
         <v>0.61</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -2844,25 +2856,25 @@
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F19" s="12">
         <v>0.7</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -2871,56 +2883,56 @@
     </row>
     <row r="20" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F20" s="12">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F21" s="12">
         <v>0.76</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2929,25 +2941,25 @@
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F22" s="12">
         <v>0.64</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -2967,112 +2979,112 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F24" s="14">
         <v>0.43</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F25" s="14">
         <v>0.44</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F26" s="14">
         <v>0.61</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F27" s="14">
         <v>0.56000000000000005</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -3092,112 +3104,112 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>174</v>
+        <v>225</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F29" s="16">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F30" s="16">
         <v>0.65</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F31" s="16">
         <v>0.65</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F32" s="16">
         <v>0.59</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -3249,25 +3261,25 @@
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6">
         <v>0.69</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -3276,56 +3288,56 @@
     </row>
     <row r="5" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>188</v>
+        <v>258</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F5" s="6">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>189</v>
+        <v>260</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F6" s="6">
         <v>0.75</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -3334,25 +3346,25 @@
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F7" s="6">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -3374,25 +3386,25 @@
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>191</v>
+        <v>262</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F9" s="8">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -3401,56 +3413,56 @@
     </row>
     <row r="10" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>65</v>
+        <v>264</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F10" s="8">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>194</v>
+        <v>265</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F11" s="8">
         <v>0.76</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -3459,25 +3471,25 @@
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F12" s="8">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -3499,25 +3511,25 @@
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F14" s="10">
         <v>0.51</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -3526,56 +3538,56 @@
     </row>
     <row r="15" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F15" s="10">
         <v>0.84</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F16" s="10">
-        <v>0.74</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -3584,25 +3596,25 @@
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F17" s="10">
         <v>0.61</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -3624,25 +3636,25 @@
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F19" s="12">
         <v>0.68</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -3651,56 +3663,56 @@
     </row>
     <row r="20" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F20" s="12">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>208</v>
+        <v>271</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F21" s="12">
         <v>0.76</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -3709,25 +3721,25 @@
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F22" s="12">
         <v>0.64</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -3747,112 +3759,112 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F24" s="14">
         <v>0.41</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F25" s="14">
         <v>0.41</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F26" s="14">
         <v>0.61</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F27" s="14">
         <v>0.56000000000000005</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -3872,112 +3884,112 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>217</v>
+        <v>53</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>218</v>
+        <v>251</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F29" s="16">
         <v>0.6</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F30" s="16">
         <v>0.65</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F31" s="16">
         <v>0.65</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F32" s="16">
         <v>0.59</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -4023,112 +4035,112 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>226</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>227</v>
+        <v>84</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6">
         <v>0.66</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>229</v>
+        <v>88</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>230</v>
+        <v>10</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F5" s="6">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>231</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F6" s="6">
         <v>0.75</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F7" s="6">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -4148,112 +4160,112 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>232</v>
+        <v>97</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>233</v>
+        <v>98</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F9" s="8">
         <v>0.69</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>234</v>
+        <v>99</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>236</v>
+        <v>101</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>237</v>
+        <v>102</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F10" s="8">
         <v>0.86</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>238</v>
+        <v>103</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F11" s="8">
         <v>0.76</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F12" s="8">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -4273,112 +4285,112 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>240</v>
+        <v>27</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>241</v>
+        <v>28</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F14" s="10">
         <v>0.63</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>244</v>
+        <v>31</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>245</v>
+        <v>32</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F15" s="10">
         <v>0.74</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>246</v>
+        <v>33</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F16" s="10">
-        <v>0.74</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F17" s="10">
         <v>0.61</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -4398,112 +4410,112 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>247</v>
+        <v>39</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>248</v>
+        <v>40</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>249</v>
+        <v>41</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F19" s="12">
         <v>0.7</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>250</v>
+        <v>42</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
     </row>
-    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>251</v>
+        <v>43</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>252</v>
+        <v>44</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>237</v>
+        <v>22</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F20" s="12">
         <v>0.86</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>253</v>
+        <v>45</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F21" s="12">
         <v>0.76</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F22" s="12">
         <v>0.64</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -4523,112 +4535,112 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>217</v>
+        <v>53</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>254</v>
+        <v>54</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F24" s="14">
         <v>0.6</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>255</v>
+        <v>56</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F25" s="14">
         <v>0.77</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>258</v>
+        <v>59</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F26" s="14">
         <v>0.61</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F27" s="14">
         <v>0.56000000000000005</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -4648,112 +4660,112 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>259</v>
+        <v>65</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>261</v>
+        <v>67</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F29" s="16">
         <v>0.57999999999999996</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>262</v>
+        <v>68</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>263</v>
+        <v>69</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>264</v>
+        <v>70</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>265</v>
+        <v>71</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F30" s="16">
         <v>0.77</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>266</v>
+        <v>72</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F31" s="16">
         <v>0.65</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F32" s="16">
         <v>0.59</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -4772,6 +4784,7 @@
   <cols>
     <col min="1" max="1" width="33.7109375" customWidth="1"/>
     <col min="7" max="7" width="24.140625" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
     <col min="11" max="11" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4798,112 +4811,112 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6">
         <v>0.64</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>269</v>
-      </c>
       <c r="C5" s="6" t="s">
-        <v>206</v>
+        <v>88</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F5" s="6">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F6" s="6">
         <v>0.75</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F7" s="6">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -4923,112 +4936,112 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F9" s="8">
         <v>0.63</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>276</v>
+        <v>141</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>269</v>
+        <v>186</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F10" s="8">
         <v>0.85</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F11" s="8">
         <v>0.76</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F12" s="8">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -5048,112 +5061,112 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D14" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>8</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>32</v>
       </c>
       <c r="F14" s="10">
         <v>0.68</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F15" s="10">
         <v>0.82</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F16" s="10">
-        <v>0.74</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F17" s="10">
         <v>0.61</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -5173,112 +5186,112 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>264</v>
+        <v>70</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F19" s="12">
         <v>0.66</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
     </row>
-    <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F20" s="12">
         <v>0.84</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F21" s="12">
         <v>0.76</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F22" s="12">
         <v>0.64</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -5298,112 +5311,112 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F24" s="14">
         <v>0.56000000000000005</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F25" s="14">
         <v>0.76</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F26" s="14">
         <v>0.61</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F27" s="14">
         <v>0.56000000000000005</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -5423,112 +5436,112 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F29" s="16">
         <v>0.6</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F30" s="16">
         <v>0.72</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F31" s="16">
         <v>0.65</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F32" s="16">
         <v>0.59</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
